--- a/data/trans_dic/P79$recibos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79$recibos_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 18,54</t>
+          <t>12,96; 18,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,91; 18,1</t>
+          <t>14,5; 18,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 17,42</t>
+          <t>14,5; 17,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,94</t>
+          <t>7,58; 10,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,84</t>
+          <t>8,33; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,9</t>
+          <t>8,28; 10,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,82</t>
+          <t>1,06; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,12</t>
+          <t>2,56; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,74</t>
+          <t>2,15; 3,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,62</t>
+          <t>7,61; 9,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,04</t>
+          <t>8,86; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,09</t>
+          <t>8,59; 9,95</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>214916</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62804; 91269</t>
+          <t>71395; 103294</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99600; 129620</t>
+          <t>113131; 146178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169427; 210520</t>
+          <t>192922; 238680</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172730</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>335056</t>
+          <t>392498</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112107; 198939</t>
+          <t>163500; 225069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123803; 206876</t>
+          <t>174535; 225992</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265268; 385081</t>
+          <t>352212; 433192</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>40028</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5859; 18053</t>
+          <t>7479; 22064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15765; 33037</t>
+          <t>18332; 39559</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25488; 48090</t>
+          <t>30556; 53523</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194955; 289529</t>
+          <t>259582; 332309</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>246733; 347745</t>
+          <t>318274; 387937</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>477763; 620045</t>
+          <t>601736; 696789</t>
         </is>
       </c>
     </row>
